--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488118_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488118_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6088</v>
+        <v>6.6607</v>
       </c>
       <c r="E2" t="n">
-        <v>7.73</v>
+        <v>7.8943</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.1212</v>
+        <v>-1.2335</v>
       </c>
       <c r="G2" t="n">
         <v>2.8864</v>
@@ -610,13 +610,13 @@
         <v>1.5858</v>
       </c>
       <c r="S2" t="n">
-        <v>1.533</v>
+        <v>1.5849</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3196</v>
+        <v>0.4838</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2134</v>
+        <v>1.1011</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5417</v>
+        <v>2.5978</v>
       </c>
       <c r="E3" t="n">
         <v>1.3252</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2165</v>
+        <v>1.2726</v>
       </c>
       <c r="G3" t="n">
         <v>1.5314</v>
@@ -688,13 +688,13 @@
         <v>2.1805</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1791</v>
+        <v>-0.1229</v>
       </c>
       <c r="T3" t="n">
         <v>0.0552</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. WOLKOWYSKI</t>
+          <t>D. TERRÓN FERNÁNDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1633</v>
+        <v>1.508</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1197</v>
+        <v>1.508</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0436</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.1483</v>
+        <v>1.508</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5936</v>
+        <v>0.3027</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5547</v>
+        <v>1.2053</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9946</v>
+        <v>1.508</v>
       </c>
       <c r="K4" t="n">
-        <v>1.191</v>
+        <v>0.3027</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8036</v>
+        <v>1.2053</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8463000000000001</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5975</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2488</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7929</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1805</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>2.1449</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4355</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7094</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.337</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. TERRÓN FERNÁNDEZ</t>
+          <t>T. WOLKOWYSKI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.508</v>
+        <v>1.1123</v>
       </c>
       <c r="E5" t="n">
-        <v>1.508</v>
+        <v>-0.7347</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.847</v>
       </c>
       <c r="G5" t="n">
-        <v>1.508</v>
+        <v>1.1483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3027</v>
+        <v>0.5936</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2053</v>
+        <v>0.5547</v>
       </c>
       <c r="J5" t="n">
-        <v>1.508</v>
+        <v>1.9946</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3027</v>
+        <v>1.191</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2053</v>
+        <v>0.8036</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-0.5975</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.2488</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.0939</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>0.5129</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.337</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.014</v>
+        <v>0.4526</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1515</v>
+        <v>0.927</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1655</v>
+        <v>-0.4744</v>
       </c>
       <c r="G6" t="n">
         <v>-1.8902</v>
@@ -922,13 +922,13 @@
         <v>2.1805</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4401</v>
+        <v>0.9067</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8587</v>
+        <v>-0.0833</v>
       </c>
       <c r="U6" t="n">
-        <v>1.2989</v>
+        <v>0.99</v>
       </c>
       <c r="V6" t="n">
         <v>-0.7444</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5343</v>
+        <v>0.4138</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0145</v>
+        <v>1.6257</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5488</v>
+        <v>-1.2119</v>
       </c>
       <c r="G7" t="n">
         <v>2.6558</v>
@@ -1000,13 +1000,13 @@
         <v>2.9733</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3794</v>
+        <v>-0.4313</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0608</v>
+        <v>-0.4495</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3187</v>
+        <v>0.0183</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8107</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. KRASTS</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.1021</v>
       </c>
       <c r="E8" t="n">
-        <v>0.919</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6574</v>
+        <v>-0.8648</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.6853</v>
+        <v>-3.1342</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2096</v>
+        <v>-0.5556</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4757</v>
+        <v>-2.5786</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1474</v>
+        <v>0.3127</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3309</v>
+        <v>1.3185</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4782</v>
+        <v>-1.0057</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.5379</v>
+        <v>-3.447</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5404</v>
+        <v>-1.8741</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.9975</v>
+        <v>-1.5729</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7929</v>
+        <v>3.3698</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>3.3698</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2353</v>
+        <v>1.473</v>
       </c>
       <c r="T8" t="n">
-        <v>3.1388</v>
+        <v>0.4499</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0965</v>
+        <v>1.0231</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0813</v>
+        <v>-1.8107</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.0813</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8107</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7872</v>
+        <v>-0.9244</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4967</v>
+        <v>-0.8023</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2905</v>
+        <v>-0.122</v>
       </c>
       <c r="G9" t="n">
         <v>-1.1419</v>
@@ -1156,13 +1156,13 @@
         <v>0.7929</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5528999999999999</v>
+        <v>0.4158</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4406</v>
+        <v>0.135</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1123</v>
+        <v>0.2808</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>N. ESCOLANO ZAVALA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6188</v>
+        <v>-1.3428</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7259</v>
+        <v>-2.4446</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8928</v>
+        <v>1.1018</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1342</v>
+        <v>-4.0067</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.5556</v>
+        <v>-3.1324</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.5786</v>
+        <v>-0.8743</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3127</v>
+        <v>-1.5519</v>
       </c>
       <c r="K10" t="n">
-        <v>1.3185</v>
+        <v>-0.9207</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0057</v>
+        <v>-0.6312</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.447</v>
+        <v>-2.4548</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8741</v>
+        <v>-2.2117</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.5729</v>
+        <v>-0.2431</v>
       </c>
       <c r="P10" t="n">
-        <v>3.3698</v>
+        <v>2.1805</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3698</v>
+        <v>3.1716</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0437</v>
+        <v>0.4131</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0387</v>
+        <v>0.0984</v>
       </c>
       <c r="U10" t="n">
-        <v>0.995</v>
+        <v>0.3147</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8107</v>
+        <v>0.0704</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8107</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. ESCOLANO ZAVALA</t>
+          <t>P. MORENO VEGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6474</v>
+        <v>-2.1505</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6088</v>
+        <v>-1.0572</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9614</v>
+        <v>-1.0932</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.0067</v>
+        <v>-0.2608</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.1324</v>
+        <v>0.1506</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8743</v>
+        <v>-0.4114</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5519</v>
+        <v>0.8066</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9207</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6312</v>
+        <v>0.1205</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.4548</v>
+        <v>-1.0674</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.2117</v>
+        <v>-0.5355</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2431</v>
+        <v>-0.5319</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1805</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R11" t="n">
-        <v>3.1716</v>
+        <v>0.7929</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1084</v>
+        <v>0.1698</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0658</v>
+        <v>0.1184</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1743</v>
+        <v>0.0514</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0704</v>
+        <v>-0.8701</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0704</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4328</v>
+        <v>-2.538</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7366</v>
+        <v>-2.5329</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3038</v>
+        <v>-0.0051</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4324</v>
@@ -1390,13 +1390,13 @@
         <v>0.7929</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7924</v>
+        <v>0.6873</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2496</v>
+        <v>-0.0459</v>
       </c>
       <c r="U12" t="n">
-        <v>1.042</v>
+        <v>0.7332</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6036</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. MORENO VEGA</t>
+          <t>A. KRASTS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5684</v>
+        <v>-2.8953</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.3629</v>
+        <v>-1.3221</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.2055</v>
+        <v>-1.5732</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2608</v>
+        <v>-3.6853</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1506</v>
+        <v>-1.2096</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4114</v>
+        <v>-2.4757</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8066</v>
+        <v>-0.1474</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.3309</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1205</v>
+        <v>-0.4782</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.0674</v>
+        <v>-3.5379</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5355</v>
+        <v>-1.5404</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5319</v>
+        <v>-1.9975</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7929</v>
+        <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2481</v>
+        <v>1.0784</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1872</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0609</v>
+        <v>0.1807</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8701</v>
+        <v>-1.0813</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-1.0813</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4805</v>
+        <v>2.7921</v>
       </c>
       <c r="E14" t="n">
-        <v>4.837000000000001</v>
+        <v>5.149000000000002</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3564</v>
+        <v>-2.3567</v>
       </c>
       <c r="G14" t="n">
         <v>-5.8216</v>
@@ -1522,10 +1522,10 @@
         <v>17.7392</v>
       </c>
       <c r="K14" t="n">
-        <v>7.8945</v>
+        <v>7.894499999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>9.844799999999999</v>
+        <v>9.844800000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-23.561</v>
@@ -1537,7 +1537,7 @@
         <v>-9.844800000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.929100000000001</v>
+        <v>7.929100000000002</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.8754</v>
@@ -1546,16 +1546,16 @@
         <v>21.8047</v>
       </c>
       <c r="S14" t="n">
-        <v>6.956699999999999</v>
+        <v>7.268700000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>1.9289</v>
+        <v>2.2408</v>
       </c>
       <c r="U14" t="n">
-        <v>5.028</v>
+        <v>5.0281</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.5838</v>
+        <v>-6.583799999999999</v>
       </c>
       <c r="W14" t="n">
         <v>-0.9555999999999998</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. DAVID ROCHA</t>
+          <t>C. RAMON PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.0882</v>
+        <v>4.1116</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1608</v>
+        <v>4.1199</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0726</v>
+        <v>-0.0083</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8165</v>
+        <v>3.6647</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8937</v>
+        <v>-0.7432</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9228</v>
+        <v>4.4079</v>
       </c>
       <c r="J15" t="n">
-        <v>7.8689</v>
+        <v>4.2197</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5582</v>
+        <v>0.2421</v>
       </c>
       <c r="L15" t="n">
-        <v>4.3107</v>
+        <v>3.9776</v>
       </c>
       <c r="M15" t="n">
-        <v>-4.0523</v>
+        <v>-0.5551</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6645</v>
+        <v>-0.9853</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.3879</v>
+        <v>0.4303</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.1982</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4002</v>
+        <v>-1.3638</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8625</v>
+        <v>-0.9194</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4623</v>
+        <v>-0.4444</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8701</v>
+        <v>1.8107</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1367</v>
+        <v>1.8107</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. RAMON PEREZ</t>
+          <t>D. DAVID ROCHA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5238</v>
+        <v>4.0451</v>
       </c>
       <c r="E16" t="n">
-        <v>3.9161</v>
+        <v>6.2627</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3923</v>
+        <v>-2.2176</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6647</v>
+        <v>3.8165</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7432</v>
+        <v>1.8937</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4079</v>
+        <v>1.9228</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2197</v>
+        <v>7.8689</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2421</v>
+        <v>3.5582</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9776</v>
+        <v>4.3107</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5551</v>
+        <v>-4.0523</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9853</v>
+        <v>-1.6645</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4303</v>
+        <v>-2.3879</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9911</v>
+        <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9515</v>
+        <v>-0.4433</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1232</v>
+        <v>-0.7607</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8283</v>
+        <v>0.3173</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8107</v>
+        <v>0.8701</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8107</v>
+        <v>1.1367</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6357</v>
+        <v>3.3638</v>
       </c>
       <c r="E17" t="n">
-        <v>3.176</v>
+        <v>3.3797</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5403</v>
+        <v>-0.0159</v>
       </c>
       <c r="G17" t="n">
         <v>4.7352</v>
@@ -1780,13 +1780,13 @@
         <v>0.9911</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1699</v>
+        <v>-1.4418</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1232</v>
+        <v>-0.9194</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0467</v>
+        <v>-0.5224</v>
       </c>
       <c r="V17" t="n">
         <v>0.0704</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.5904</v>
+        <v>2.6165</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4351</v>
+        <v>1.6389</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1553</v>
+        <v>0.9776</v>
       </c>
       <c r="G18" t="n">
         <v>2.0032</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0779</v>
+        <v>-1.0518</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1232</v>
+        <v>-0.9194</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0452</v>
+        <v>-0.1324</v>
       </c>
       <c r="V18" t="n">
         <v>0.674</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. YELAMOS MAÑAS</t>
+          <t>A. RODRIGUEZ VILLEGAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.0186</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.7672</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6052999999999999</v>
+        <v>-0.0887</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6052999999999999</v>
+        <v>1.0152</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.104</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.4745</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6052999999999999</v>
+        <v>0.3903</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.0842</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>-0.5633</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.1882</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.3876</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0.3415</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.2844</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.0571</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ VILLEGAS</t>
+          <t>J. YELAMOS MAÑAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3901</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1852</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5753</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0887</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0152</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.104</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4745</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3903</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0842</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5633</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.625</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1882</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.5947</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7372</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4881</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.249</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2242</v>
+        <v>-0.6424</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0795</v>
+        <v>-1.7739</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8552999999999999</v>
+        <v>1.1315</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3224</v>
@@ -2092,13 +2092,13 @@
         <v>1.1893</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.316</v>
+        <v>-0.7342</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8736</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4425</v>
+        <v>-0.1662</v>
       </c>
       <c r="V21" t="n">
         <v>1.2071</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5059</v>
+        <v>-1.5308</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1498</v>
+        <v>-1.4554</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3561</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>-2.859</v>
@@ -2170,13 +2170,13 @@
         <v>1.5858</v>
       </c>
       <c r="S22" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.0596</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4406</v>
+        <v>0.135</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3561</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.674</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0549</v>
+        <v>-3.0477</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4197</v>
+        <v>-2.216</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6352</v>
+        <v>-0.8317</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0223</v>
@@ -2248,13 +2248,13 @@
         <v>1.784</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1479</v>
+        <v>0.155</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4257</v>
+        <v>-0.222</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5736</v>
+        <v>0.3771</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8131</v>
+        <v>-5.1749</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6335</v>
+        <v>-4.9391</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1796</v>
+        <v>-0.2358</v>
       </c>
       <c r="G24" t="n">
         <v>-1.933</v>
@@ -2326,13 +2326,13 @@
         <v>1.784</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6086</v>
+        <v>0.2468</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2534</v>
+        <v>-0.0522</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3552</v>
+        <v>0.2991</v>
       </c>
       <c r="V24" t="n">
         <v>0.674</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7157</v>
+        <v>-6.2544</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4691</v>
+        <v>-3.2841</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2466</v>
+        <v>-2.9704</v>
       </c>
       <c r="G25" t="n">
         <v>-2.7779</v>
@@ -2404,13 +2404,13 @@
         <v>1.3876</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.145</v>
+        <v>-0.6837</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2975</v>
+        <v>-0.5174</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4425</v>
+        <v>-0.1662</v>
       </c>
       <c r="V25" t="n">
         <v>-1.2071</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.4803</v>
+        <v>-1.122099999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>2.356500000000001</v>
+        <v>2.356599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.8368</v>
+        <v>-3.4787</v>
       </c>
       <c r="G26" t="n">
         <v>5.821600000000001</v>
@@ -2482,13 +2482,13 @@
         <v>13.8756</v>
       </c>
       <c r="S26" t="n">
-        <v>-6.956700000000001</v>
+        <v>-5.598699999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>-5.028</v>
+        <v>-5.027900000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.9288</v>
+        <v>-0.5704999999999998</v>
       </c>
       <c r="V26" t="n">
         <v>6.5839</v>
